--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ30"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129616503</v>
+        <v>136774567</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>92789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,42 +810,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580694</v>
+        <v>580679</v>
       </c>
       <c r="R3" t="n">
-        <v>6400829</v>
+        <v>6400898</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,22 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,30 +889,31 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129616503</t>
+          <t>https://artportalen.se/Sighting/136774567</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129617936</v>
+        <v>129616503</v>
       </c>
       <c r="B4" t="n">
         <v>57950</v>
@@ -952,17 +949,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Slissjön, Stora Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580617</v>
+        <v>580694</v>
       </c>
       <c r="R4" t="n">
-        <v>6400527</v>
+        <v>6400829</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,13 +1024,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129617936</t>
+          <t>https://artportalen.se/Sighting/129616503</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129620476</v>
+        <v>129617936</v>
       </c>
       <c r="B5" t="n">
         <v>57950</v>
@@ -1069,17 +1066,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>Stora Slissjön, Stora Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580724</v>
+        <v>580617</v>
       </c>
       <c r="R5" t="n">
-        <v>6400808</v>
+        <v>6400527</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,13 +1141,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129620476</t>
+          <t>https://artportalen.se/Sighting/129617936</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129678927</v>
+        <v>129620476</v>
       </c>
       <c r="B6" t="n">
         <v>57950</v>
@@ -1179,27 +1176,24 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580747</v>
+        <v>580724</v>
       </c>
       <c r="R6" t="n">
-        <v>6400822</v>
+        <v>6400808</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,12 +1217,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,24 +1247,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129678927</t>
+          <t>https://artportalen.se/Sighting/129620476</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129716919</v>
+        <v>129678927</v>
       </c>
       <c r="B7" t="n">
         <v>57950</v>
@@ -1289,24 +1293,27 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stora Slissjön, Stora Slissjön, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580568</v>
+        <v>580747</v>
       </c>
       <c r="R7" t="n">
-        <v>6400615</v>
+        <v>6400822</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,22 +1337,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:27</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:27</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,27 +1357,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129716919</t>
+          <t>https://artportalen.se/Sighting/129678927</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129678798</v>
+        <v>129716919</v>
       </c>
       <c r="B8" t="n">
-        <v>57132</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,16 +1385,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1405,28 +1402,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Stora Slissjön, Stora Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580682</v>
+        <v>580568</v>
       </c>
       <c r="R8" t="n">
-        <v>6400886</v>
+        <v>6400615</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,24 +1444,29 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Uppflog, ngt osäker men tyckte bullret var arttypiskt!</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1475,27 +1474,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129678798</t>
+          <t>https://artportalen.se/Sighting/129716919</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129616677</v>
+        <v>136774732</v>
       </c>
       <c r="B9" t="n">
-        <v>58327</v>
+        <v>57313</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,16 +1502,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>100065</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1521,19 +1520,27 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>sträckande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580709</v>
+        <v>580669</v>
       </c>
       <c r="R9" t="n">
-        <v>6400795</v>
+        <v>6400924</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,22 +1564,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>En flock hörd sträcka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,27 +1599,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129616677</t>
+          <t>https://artportalen.se/Sighting/136774732</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129617269</v>
+        <v>129678798</v>
       </c>
       <c r="B10" t="n">
-        <v>58327</v>
+        <v>57132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,16 +1627,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1632,17 +1644,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Slissjön, Stora Slissjön, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580623</v>
+        <v>580682</v>
       </c>
       <c r="R10" t="n">
-        <v>6400588</v>
+        <v>6400886</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1669,29 +1689,24 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:06</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:06</t>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Uppflog, ngt osäker men tyckte bullret var arttypiskt!</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -1699,24 +1714,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129617269</t>
+          <t>https://artportalen.se/Sighting/129678798</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129716635</v>
+        <v>129616677</v>
       </c>
       <c r="B11" t="n">
         <v>58327</v>
@@ -1747,14 +1762,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stora Slissjön, Stora Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580602</v>
+        <v>580709</v>
       </c>
       <c r="R11" t="n">
-        <v>6400630</v>
+        <v>6400795</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1781,22 +1796,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,60 +1837,51 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129716635</t>
+          <t>https://artportalen.se/Sighting/129616677</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617357</v>
+        <v>129617269</v>
       </c>
       <c r="B12" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stora Slissjön, Stora Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580613</v>
+        <v>580623</v>
       </c>
       <c r="R12" t="n">
-        <v>6400571</v>
+        <v>6400588</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1907,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1917,7 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,63 +1949,51 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129617357</t>
+          <t>https://artportalen.se/Sighting/129617269</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129678786</v>
+        <v>129716635</v>
       </c>
       <c r="B13" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Stora Slissjön, Stora Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580682</v>
+        <v>580602</v>
       </c>
       <c r="R13" t="n">
-        <v>6400886</v>
+        <v>6400630</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2026,12 +2020,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,24 +2050,24 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129678786</t>
+          <t>https://artportalen.se/Sighting/129716635</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129716000</v>
+        <v>129617357</v>
       </c>
       <c r="B14" t="n">
         <v>58114</v>
@@ -2091,7 +2095,11 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
@@ -2099,14 +2107,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>Stora Slissjön, Stora Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580679</v>
+        <v>580613</v>
       </c>
       <c r="R14" t="n">
-        <v>6400859</v>
+        <v>6400571</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2133,22 +2141,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,54 +2182,66 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129716000</t>
+          <t>https://artportalen.se/Sighting/129617357</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129616134</v>
+        <v>129678786</v>
       </c>
       <c r="B15" t="n">
-        <v>111175</v>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219677</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580684</v>
+        <v>580682</v>
       </c>
       <c r="R15" t="n">
-        <v>6400847</v>
+        <v>6400886</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2245,22 +2265,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,59 +2285,55 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129616134</t>
+          <t>https://artportalen.se/Sighting/129678786</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129616302</v>
+        <v>129716000</v>
       </c>
       <c r="B16" t="n">
-        <v>111175</v>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219677</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2336,13 +2342,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580685</v>
+        <v>580679</v>
       </c>
       <c r="R16" t="n">
-        <v>6400840</v>
+        <v>6400859</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2366,22 +2372,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,54 +2413,66 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129616302</t>
+          <t>https://artportalen.se/Sighting/129716000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129616552</v>
+        <v>136774596</v>
       </c>
       <c r="B17" t="n">
-        <v>111175</v>
+        <v>58169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219677</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
         <v>580692</v>
       </c>
       <c r="R17" t="n">
-        <v>6400823</v>
+        <v>6400939</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2478,22 +2496,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,27 +2516,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129616552</t>
+          <t>https://artportalen.se/Sighting/136774596</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129620441</v>
+        <v>136774602</v>
       </c>
       <c r="B18" t="n">
-        <v>111175</v>
+        <v>58164</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,37 +2544,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219677</v>
+        <v>103023</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580732</v>
+        <v>580692</v>
       </c>
       <c r="R18" t="n">
-        <v>6400807</v>
+        <v>6400939</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2590,22 +2606,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,24 +2626,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129620441</t>
+          <t>https://artportalen.se/Sighting/136774602</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129620499</v>
+        <v>129616134</v>
       </c>
       <c r="B19" t="n">
         <v>111175</v>
@@ -2672,13 +2678,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580735</v>
+        <v>580684</v>
       </c>
       <c r="R19" t="n">
-        <v>6400802</v>
+        <v>6400847</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2707,7 +2713,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2717,7 +2723,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,43 +2749,43 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129620499</t>
+          <t>https://artportalen.se/Sighting/129616134</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129616252</v>
+        <v>129616302</v>
       </c>
       <c r="B20" t="n">
-        <v>99118</v>
+        <v>111175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2793,10 +2799,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580686</v>
+        <v>580685</v>
       </c>
       <c r="R20" t="n">
-        <v>6400843</v>
+        <v>6400840</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2828,7 +2834,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2838,7 +2844,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2864,63 +2870,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129616252</t>
+          <t>https://artportalen.se/Sighting/129616302</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129616400</v>
+        <v>129616552</v>
       </c>
       <c r="B21" t="n">
-        <v>99118</v>
+        <v>111175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580691</v>
+        <v>580692</v>
       </c>
       <c r="R21" t="n">
-        <v>6400838</v>
+        <v>6400823</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2949,7 +2946,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2959,7 +2956,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2985,60 +2982,51 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129616400</t>
+          <t>https://artportalen.se/Sighting/129616552</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129617115</v>
+        <v>129620441</v>
       </c>
       <c r="B22" t="n">
-        <v>99118</v>
+        <v>111175</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stora Slissjön, Stora Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580616</v>
+        <v>580732</v>
       </c>
       <c r="R22" t="n">
-        <v>6400632</v>
+        <v>6400807</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -3070,7 +3058,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3080,7 +3068,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3106,62 +3094,54 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129617115</t>
+          <t>https://artportalen.se/Sighting/129620441</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129678855</v>
+        <v>129620499</v>
       </c>
       <c r="B23" t="n">
-        <v>99118</v>
+        <v>111175</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580710</v>
+        <v>580735</v>
       </c>
       <c r="R23" t="n">
-        <v>6400826</v>
+        <v>6400802</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3185,12 +3165,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,31 +3189,30 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129678855</t>
+          <t>https://artportalen.se/Sighting/129620499</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129678892</v>
+        <v>129616252</v>
       </c>
       <c r="B24" t="n">
         <v>99118</v>
@@ -3253,7 +3242,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3261,22 +3250,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580736</v>
+        <v>580686</v>
       </c>
       <c r="R24" t="n">
-        <v>6400804</v>
+        <v>6400843</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3300,12 +3286,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3314,31 +3310,30 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129678892</t>
+          <t>https://artportalen.se/Sighting/129616252</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129679791</v>
+        <v>129616400</v>
       </c>
       <c r="B25" t="n">
         <v>99118</v>
@@ -3366,28 +3361,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580667</v>
+        <v>580691</v>
       </c>
       <c r="R25" t="n">
-        <v>6400917</v>
+        <v>6400838</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3411,12 +3407,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3425,31 +3431,30 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129679791</t>
+          <t>https://artportalen.se/Sighting/129616400</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129679797</v>
+        <v>129617115</v>
       </c>
       <c r="B26" t="n">
         <v>99118</v>
@@ -3477,28 +3482,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Stora Slissjön, Stora Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580677</v>
+        <v>580616</v>
       </c>
       <c r="R26" t="n">
-        <v>6400916</v>
+        <v>6400632</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3522,12 +3528,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3536,31 +3552,30 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129679797</t>
+          <t>https://artportalen.se/Sighting/129617115</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129679800</v>
+        <v>129678855</v>
       </c>
       <c r="B27" t="n">
         <v>99118</v>
@@ -3603,10 +3618,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580657</v>
+        <v>580710</v>
       </c>
       <c r="R27" t="n">
-        <v>6400934</v>
+        <v>6400826</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3659,19 +3674,19 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129679800</t>
+          <t>https://artportalen.se/Sighting/129678855</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129679808</v>
+        <v>129678892</v>
       </c>
       <c r="B28" t="n">
         <v>99118</v>
@@ -3699,7 +3714,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -3714,10 +3733,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580686</v>
+        <v>580736</v>
       </c>
       <c r="R28" t="n">
-        <v>6400878</v>
+        <v>6400804</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3770,69 +3789,68 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129679808</t>
+          <t>https://artportalen.se/Sighting/129678892</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129616666</v>
+        <v>129679791</v>
       </c>
       <c r="B29" t="n">
-        <v>101325</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580709</v>
+        <v>580667</v>
       </c>
       <c r="R29" t="n">
-        <v>6400795</v>
+        <v>6400917</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3856,22 +3874,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,71 +3888,80 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129616666</t>
+          <t>https://artportalen.se/Sighting/129679791</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129617462</v>
+        <v>129679797</v>
       </c>
       <c r="B30" t="n">
-        <v>101325</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stora Slissjön, Stora Slissjön, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580609</v>
+        <v>580677</v>
       </c>
       <c r="R30" t="n">
-        <v>6400573</v>
+        <v>6400916</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3968,22 +3985,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3992,22 +3999,1743 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129679797</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129679800</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>580657</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6400934</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129679800</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129679808</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>580686</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6400878</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129679808</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136774259</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>580666</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6400927</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136774259</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136774284</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>580670</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6400928</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136774284</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136774318</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>580663</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6400930</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136774318</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136774328</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>580647</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6400923</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136774328</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136774398</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>580662</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6400928</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136774398</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136774429</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>580656</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6400938</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136774429</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136774444</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>580676</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6400938</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136774444</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136774456</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>580661</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6400922</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136774456</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136774518</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>580692</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6400939</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136774518</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136774539</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>580688</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6400932</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136774539</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136774579</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>580677</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6400915</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136774579</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129616666</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>580709</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6400795</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129616666</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129617462</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stora Slissjön, Stora Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>580609</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6400573</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129617462</t>
         </is>
@@ -4044,6 +5772,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ45"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2533,40 +2533,44 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136774602</v>
+        <v>136819177</v>
       </c>
       <c r="B18" t="n">
-        <v>58164</v>
+        <v>58169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2576,10 +2580,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580692</v>
+        <v>580702</v>
       </c>
       <c r="R18" t="n">
-        <v>6400939</v>
+        <v>6400831</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2606,12 +2610,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,60 +2635,72 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774602</t>
+          <t>https://artportalen.se/Sighting/136819177</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129616134</v>
+        <v>136819277</v>
       </c>
       <c r="B19" t="n">
-        <v>111175</v>
+        <v>58169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219677</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580684</v>
+        <v>580732</v>
       </c>
       <c r="R19" t="n">
-        <v>6400847</v>
+        <v>6400796</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2708,22 +2724,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,74 +2744,77 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129616134</t>
+          <t>https://artportalen.se/Sighting/136819277</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129616302</v>
+        <v>136819371</v>
       </c>
       <c r="B20" t="n">
-        <v>111175</v>
+        <v>58169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219677</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580685</v>
+        <v>580293</v>
       </c>
       <c r="R20" t="n">
-        <v>6400840</v>
+        <v>6400978</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2829,22 +2838,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2859,65 +2858,77 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129616302</t>
+          <t>https://artportalen.se/Sighting/136819371</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129616552</v>
+        <v>136819405</v>
       </c>
       <c r="B21" t="n">
-        <v>111175</v>
+        <v>58169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219677</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580692</v>
+        <v>580723</v>
       </c>
       <c r="R21" t="n">
-        <v>6400823</v>
+        <v>6400746</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2941,22 +2952,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2971,65 +2972,77 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129616552</t>
+          <t>https://artportalen.se/Sighting/136819405</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129620441</v>
+        <v>136819440</v>
       </c>
       <c r="B22" t="n">
-        <v>111175</v>
+        <v>58169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219677</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580732</v>
+        <v>580640</v>
       </c>
       <c r="R22" t="n">
-        <v>6400807</v>
+        <v>6400560</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3053,22 +3066,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3083,27 +3086,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129620441</t>
+          <t>https://artportalen.se/Sighting/136819440</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129620499</v>
+        <v>136774602</v>
       </c>
       <c r="B23" t="n">
-        <v>111175</v>
+        <v>58164</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3111,37 +3114,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219677</v>
+        <v>103023</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580735</v>
+        <v>580692</v>
       </c>
       <c r="R23" t="n">
-        <v>6400802</v>
+        <v>6400939</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3165,22 +3176,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3195,74 +3196,65 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129620499</t>
+          <t>https://artportalen.se/Sighting/136774602</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129616252</v>
+        <v>129616134</v>
       </c>
       <c r="B24" t="n">
-        <v>99118</v>
+        <v>111175</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580686</v>
+        <v>580684</v>
       </c>
       <c r="R24" t="n">
-        <v>6400843</v>
+        <v>6400847</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3291,7 +3283,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3301,7 +3293,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3327,43 +3319,43 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129616252</t>
+          <t>https://artportalen.se/Sighting/129616134</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129616400</v>
+        <v>129616302</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>111175</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3377,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580691</v>
+        <v>580685</v>
       </c>
       <c r="R25" t="n">
-        <v>6400838</v>
+        <v>6400840</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3412,7 +3404,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3422,7 +3414,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3448,60 +3440,51 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129616400</t>
+          <t>https://artportalen.se/Sighting/129616302</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129617115</v>
+        <v>129616552</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>111175</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stora Slissjön, Stora Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580616</v>
+        <v>580692</v>
       </c>
       <c r="R26" t="n">
-        <v>6400632</v>
+        <v>6400823</v>
       </c>
       <c r="S26" t="n">
         <v>2</v>
@@ -3533,7 +3516,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3543,7 +3526,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3569,62 +3552,54 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129617115</t>
+          <t>https://artportalen.se/Sighting/129616552</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129678855</v>
+        <v>129620441</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>111175</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580710</v>
+        <v>580732</v>
       </c>
       <c r="R27" t="n">
-        <v>6400826</v>
+        <v>6400807</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3648,12 +3623,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3662,84 +3647,71 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129678855</t>
+          <t>https://artportalen.se/Sighting/129620441</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129678892</v>
+        <v>129620499</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>111175</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580736</v>
+        <v>580735</v>
       </c>
       <c r="R28" t="n">
-        <v>6400804</v>
+        <v>6400802</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3763,12 +3735,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3777,56 +3759,55 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Eddy Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129678892</t>
+          <t>https://artportalen.se/Sighting/129620499</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129679791</v>
+        <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>99118</v>
+        <v>111435</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3844,13 +3825,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580667</v>
+        <v>580702</v>
       </c>
       <c r="R29" t="n">
-        <v>6400917</v>
+        <v>6400831</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3874,12 +3855,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3900,44 +3881,44 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129679791</t>
+          <t>https://artportalen.se/Sighting/136819156</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129679797</v>
+        <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>99118</v>
+        <v>111435</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3955,10 +3936,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580677</v>
+        <v>580686</v>
       </c>
       <c r="R30" t="n">
-        <v>6400916</v>
+        <v>6400820</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3985,12 +3966,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4011,19 +3992,19 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129679797</t>
+          <t>https://artportalen.se/Sighting/136819298</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129679800</v>
+        <v>129616252</v>
       </c>
       <c r="B31" t="n">
         <v>99118</v>
@@ -4051,28 +4032,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580657</v>
+        <v>580686</v>
       </c>
       <c r="R31" t="n">
-        <v>6400934</v>
+        <v>6400843</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4096,12 +4078,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4110,31 +4102,30 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129679800</t>
+          <t>https://artportalen.se/Sighting/129616252</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129679808</v>
+        <v>129616400</v>
       </c>
       <c r="B32" t="n">
         <v>99118</v>
@@ -4162,28 +4153,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580686</v>
+        <v>580691</v>
       </c>
       <c r="R32" t="n">
-        <v>6400878</v>
+        <v>6400838</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4207,12 +4199,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4221,34 +4223,33 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129679808</t>
+          <t>https://artportalen.se/Sighting/129616400</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136774259</v>
+        <v>129617115</v>
       </c>
       <c r="B33" t="n">
-        <v>99351</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4275,7 +4276,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4283,22 +4284,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 51234, St Slissjön, Sm</t>
+          <t>Stora Slissjön, Stora Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580666</v>
+        <v>580616</v>
       </c>
       <c r="R33" t="n">
-        <v>6400927</v>
+        <v>6400632</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4322,12 +4320,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4336,34 +4344,33 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774259</t>
+          <t>https://artportalen.se/Sighting/129617115</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136774284</v>
+        <v>129678855</v>
       </c>
       <c r="B34" t="n">
-        <v>99351</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4388,11 +4395,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -4407,10 +4410,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580670</v>
+        <v>580710</v>
       </c>
       <c r="R34" t="n">
-        <v>6400928</v>
+        <v>6400826</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4437,12 +4440,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4463,22 +4466,22 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774284</t>
+          <t>https://artportalen.se/Sighting/129678855</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136774318</v>
+        <v>129678892</v>
       </c>
       <c r="B35" t="n">
-        <v>99351</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4505,7 +4508,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4522,10 +4525,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580663</v>
+        <v>580736</v>
       </c>
       <c r="R35" t="n">
-        <v>6400930</v>
+        <v>6400804</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4552,12 +4555,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4578,22 +4581,22 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774318</t>
+          <t>https://artportalen.se/Sighting/129678892</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136774328</v>
+        <v>129679791</v>
       </c>
       <c r="B36" t="n">
-        <v>99351</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4618,11 +4621,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -4637,10 +4636,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580647</v>
+        <v>580667</v>
       </c>
       <c r="R36" t="n">
-        <v>6400923</v>
+        <v>6400917</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4667,12 +4666,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4699,16 +4698,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774328</t>
+          <t>https://artportalen.se/Sighting/129679791</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136774398</v>
+        <v>129679797</v>
       </c>
       <c r="B37" t="n">
-        <v>99351</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4733,11 +4732,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -4752,10 +4747,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580662</v>
+        <v>580677</v>
       </c>
       <c r="R37" t="n">
-        <v>6400928</v>
+        <v>6400916</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4782,12 +4777,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4814,16 +4809,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774398</t>
+          <t>https://artportalen.se/Sighting/129679797</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136774429</v>
+        <v>129679800</v>
       </c>
       <c r="B38" t="n">
-        <v>99351</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4848,11 +4843,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -4867,10 +4858,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580656</v>
+        <v>580657</v>
       </c>
       <c r="R38" t="n">
-        <v>6400938</v>
+        <v>6400934</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4897,12 +4888,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4929,16 +4920,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774429</t>
+          <t>https://artportalen.se/Sighting/129679800</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136774444</v>
+        <v>129679808</v>
       </c>
       <c r="B39" t="n">
-        <v>99351</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4963,11 +4954,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -4982,10 +4969,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580676</v>
+        <v>580686</v>
       </c>
       <c r="R39" t="n">
-        <v>6400938</v>
+        <v>6400878</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5012,12 +4999,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5044,13 +5031,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774444</t>
+          <t>https://artportalen.se/Sighting/129679808</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136774456</v>
+        <v>136774259</v>
       </c>
       <c r="B40" t="n">
         <v>99351</v>
@@ -5080,7 +5067,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5097,10 +5084,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580661</v>
+        <v>580666</v>
       </c>
       <c r="R40" t="n">
-        <v>6400922</v>
+        <v>6400927</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5159,13 +5146,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774456</t>
+          <t>https://artportalen.se/Sighting/136774259</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136774518</v>
+        <v>136774284</v>
       </c>
       <c r="B41" t="n">
         <v>99351</v>
@@ -5195,7 +5182,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5212,10 +5199,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580692</v>
+        <v>580670</v>
       </c>
       <c r="R41" t="n">
-        <v>6400939</v>
+        <v>6400928</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5274,13 +5261,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774518</t>
+          <t>https://artportalen.se/Sighting/136774284</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136774539</v>
+        <v>136774318</v>
       </c>
       <c r="B42" t="n">
         <v>99351</v>
@@ -5310,7 +5297,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5327,10 +5314,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580688</v>
+        <v>580663</v>
       </c>
       <c r="R42" t="n">
-        <v>6400932</v>
+        <v>6400930</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5389,13 +5376,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774539</t>
+          <t>https://artportalen.se/Sighting/136774318</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136774579</v>
+        <v>136774328</v>
       </c>
       <c r="B43" t="n">
         <v>99351</v>
@@ -5442,10 +5429,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580677</v>
+        <v>580647</v>
       </c>
       <c r="R43" t="n">
-        <v>6400915</v>
+        <v>6400923</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5504,43 +5491,43 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136774579</t>
+          <t>https://artportalen.se/Sighting/136774328</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129616666</v>
+        <v>136774398</v>
       </c>
       <c r="B44" t="n">
-        <v>101325</v>
+        <v>99351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5548,19 +5535,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580709</v>
+        <v>580662</v>
       </c>
       <c r="R44" t="n">
-        <v>6400795</v>
+        <v>6400928</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5584,22 +5574,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5608,71 +5588,84 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129616666</t>
+          <t>https://artportalen.se/Sighting/136774398</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129617462</v>
+        <v>136774429</v>
       </c>
       <c r="B45" t="n">
-        <v>101325</v>
+        <v>99351</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stora Slissjön, Stora Slissjön, Sm</t>
+          <t>A 51234, St Slissjön, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580609</v>
+        <v>580656</v>
       </c>
       <c r="R45" t="n">
-        <v>6400573</v>
+        <v>6400938</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5696,22 +5689,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5720,22 +5703,1402 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136774429</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136774444</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>580676</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6400938</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136774444</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136774456</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>580661</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6400922</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136774456</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136774518</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>580692</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6400939</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136774518</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136774539</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>580688</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6400932</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136774539</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>136774579</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>580677</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6400915</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136774579</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136819122</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>580684</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6400807</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136819122</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136819195</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>580712</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6400813</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136819195</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136819203</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>580713</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6400808</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136819203</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136819212</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>580711</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6400802</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136819212</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136819236</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99351</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>A 51234, St Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>580613</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6400640</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136819236</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129616666</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kvarnkärret, Kvarnkärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>580709</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6400795</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129616666</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129617462</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Stora Slissjön, Stora Slissjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>580609</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6400573</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129617462</t>
         </is>
@@ -5787,6 +7150,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136774567</v>
       </c>
       <c r="B3" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>111435</v>
+        <v>111437</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>111435</v>
+        <v>111437</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>136774259</v>
       </c>
       <c r="B40" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>136774284</v>
       </c>
       <c r="B41" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>136774318</v>
       </c>
       <c r="B42" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>136774328</v>
       </c>
       <c r="B43" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>136774398</v>
       </c>
       <c r="B44" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>136774429</v>
       </c>
       <c r="B45" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>136774444</v>
       </c>
       <c r="B46" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>136774456</v>
       </c>
       <c r="B47" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>136774518</v>
       </c>
       <c r="B48" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>136774539</v>
       </c>
       <c r="B49" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>136774579</v>
       </c>
       <c r="B50" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>136819122</v>
       </c>
       <c r="B51" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136819195</v>
       </c>
       <c r="B52" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>136819203</v>
       </c>
       <c r="B53" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136819212</v>
       </c>
       <c r="B54" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>136819236</v>
       </c>
       <c r="B55" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136774567</v>
       </c>
       <c r="B3" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3785,7 +3785,7 @@
         <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>111437</v>
+        <v>111443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>111437</v>
+        <v>111443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>136774259</v>
       </c>
       <c r="B40" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>136774284</v>
       </c>
       <c r="B41" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>136774318</v>
       </c>
       <c r="B42" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>136774328</v>
       </c>
       <c r="B43" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>136774398</v>
       </c>
       <c r="B44" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>136774429</v>
       </c>
       <c r="B45" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>136774444</v>
       </c>
       <c r="B46" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>136774456</v>
       </c>
       <c r="B47" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>136774518</v>
       </c>
       <c r="B48" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>136774539</v>
       </c>
       <c r="B49" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>136774579</v>
       </c>
       <c r="B50" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>136819122</v>
       </c>
       <c r="B51" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136819195</v>
       </c>
       <c r="B52" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>136819203</v>
       </c>
       <c r="B53" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136819212</v>
       </c>
       <c r="B54" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>136819236</v>
       </c>
       <c r="B55" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136774567</v>
       </c>
       <c r="B3" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>111443</v>
+        <v>111445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>111443</v>
+        <v>111445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>136774259</v>
       </c>
       <c r="B40" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>136774284</v>
       </c>
       <c r="B41" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>136774318</v>
       </c>
       <c r="B42" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>136774328</v>
       </c>
       <c r="B43" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>136774398</v>
       </c>
       <c r="B44" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>136774429</v>
       </c>
       <c r="B45" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>136774444</v>
       </c>
       <c r="B46" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>136774456</v>
       </c>
       <c r="B47" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>136774518</v>
       </c>
       <c r="B48" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>136774539</v>
       </c>
       <c r="B49" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>136774579</v>
       </c>
       <c r="B50" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>136819122</v>
       </c>
       <c r="B51" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136819195</v>
       </c>
       <c r="B52" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>136819203</v>
       </c>
       <c r="B53" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136819212</v>
       </c>
       <c r="B54" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>136819236</v>
       </c>
       <c r="B55" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136774567</v>
       </c>
       <c r="B3" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>111445</v>
+        <v>111446</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>111445</v>
+        <v>111446</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>136774259</v>
       </c>
       <c r="B40" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>136774284</v>
       </c>
       <c r="B41" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>136774318</v>
       </c>
       <c r="B42" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>136774328</v>
       </c>
       <c r="B43" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>136774398</v>
       </c>
       <c r="B44" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>136774429</v>
       </c>
       <c r="B45" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>136774444</v>
       </c>
       <c r="B46" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>136774456</v>
       </c>
       <c r="B47" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>136774518</v>
       </c>
       <c r="B48" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>136774539</v>
       </c>
       <c r="B49" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>136774579</v>
       </c>
       <c r="B50" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>136819122</v>
       </c>
       <c r="B51" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136819195</v>
       </c>
       <c r="B52" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>136819203</v>
       </c>
       <c r="B53" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136819212</v>
       </c>
       <c r="B54" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>136819236</v>
       </c>
       <c r="B55" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136774567</v>
       </c>
       <c r="B3" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>111446</v>
+        <v>111452</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>111446</v>
+        <v>111452</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>136774259</v>
       </c>
       <c r="B40" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>136774284</v>
       </c>
       <c r="B41" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>136774318</v>
       </c>
       <c r="B42" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>136774328</v>
       </c>
       <c r="B43" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>136774398</v>
       </c>
       <c r="B44" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>136774429</v>
       </c>
       <c r="B45" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>136774444</v>
       </c>
       <c r="B46" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>136774456</v>
       </c>
       <c r="B47" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>136774518</v>
       </c>
       <c r="B48" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>136774539</v>
       </c>
       <c r="B49" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>136774579</v>
       </c>
       <c r="B50" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>136819122</v>
       </c>
       <c r="B51" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136819195</v>
       </c>
       <c r="B52" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>136819203</v>
       </c>
       <c r="B53" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136819212</v>
       </c>
       <c r="B54" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>136819236</v>
       </c>
       <c r="B55" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136774567</v>
       </c>
       <c r="B3" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>111452</v>
+        <v>111456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>111452</v>
+        <v>111456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>136774259</v>
       </c>
       <c r="B40" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>136774284</v>
       </c>
       <c r="B41" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>136774318</v>
       </c>
       <c r="B42" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>136774328</v>
       </c>
       <c r="B43" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>136774398</v>
       </c>
       <c r="B44" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>136774429</v>
       </c>
       <c r="B45" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>136774444</v>
       </c>
       <c r="B46" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>136774456</v>
       </c>
       <c r="B47" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>136774518</v>
       </c>
       <c r="B48" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>136774539</v>
       </c>
       <c r="B49" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>136774579</v>
       </c>
       <c r="B50" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>136819122</v>
       </c>
       <c r="B51" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136819195</v>
       </c>
       <c r="B52" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>136819203</v>
       </c>
       <c r="B53" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136819212</v>
       </c>
       <c r="B54" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>136819236</v>
       </c>
       <c r="B55" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -3785,7 +3785,7 @@
         <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>111456</v>
+        <v>111458</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>111456</v>
+        <v>111458</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>136774259</v>
       </c>
       <c r="B40" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>136774284</v>
       </c>
       <c r="B41" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>136774318</v>
       </c>
       <c r="B42" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>136774328</v>
       </c>
       <c r="B43" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>136774398</v>
       </c>
       <c r="B44" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>136774429</v>
       </c>
       <c r="B45" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>136774444</v>
       </c>
       <c r="B46" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>136774456</v>
       </c>
       <c r="B47" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>136774518</v>
       </c>
       <c r="B48" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>136774539</v>
       </c>
       <c r="B49" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>136774579</v>
       </c>
       <c r="B50" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>136819122</v>
       </c>
       <c r="B51" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136819195</v>
       </c>
       <c r="B52" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>136819203</v>
       </c>
       <c r="B53" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136819212</v>
       </c>
       <c r="B54" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>136819236</v>
       </c>
       <c r="B55" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136774567</v>
       </c>
       <c r="B3" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>111458</v>
+        <v>111460</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>111458</v>
+        <v>111460</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>136774259</v>
       </c>
       <c r="B40" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>136774284</v>
       </c>
       <c r="B41" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>136774318</v>
       </c>
       <c r="B42" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>136774328</v>
       </c>
       <c r="B43" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>136774398</v>
       </c>
       <c r="B44" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>136774429</v>
       </c>
       <c r="B45" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>136774444</v>
       </c>
       <c r="B46" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>136774456</v>
       </c>
       <c r="B47" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>136774518</v>
       </c>
       <c r="B48" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>136774539</v>
       </c>
       <c r="B49" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>136774579</v>
       </c>
       <c r="B50" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>136819122</v>
       </c>
       <c r="B51" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136819195</v>
       </c>
       <c r="B52" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>136819203</v>
       </c>
       <c r="B53" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136819212</v>
       </c>
       <c r="B54" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>136819236</v>
       </c>
       <c r="B55" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136774567</v>
       </c>
       <c r="B3" t="n">
-        <v>92808</v>
+        <v>92821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>136774732</v>
       </c>
       <c r="B9" t="n">
-        <v>57313</v>
+        <v>57326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136774596</v>
       </c>
       <c r="B17" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136819177</v>
       </c>
       <c r="B18" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>136819277</v>
       </c>
       <c r="B19" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>136819371</v>
       </c>
       <c r="B20" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>136819405</v>
       </c>
       <c r="B21" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>136819440</v>
       </c>
       <c r="B22" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>136774602</v>
       </c>
       <c r="B23" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>111460</v>
+        <v>111473</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>111460</v>
+        <v>111473</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>136774259</v>
       </c>
       <c r="B40" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>136774284</v>
       </c>
       <c r="B41" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>136774318</v>
       </c>
       <c r="B42" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>136774328</v>
       </c>
       <c r="B43" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>136774398</v>
       </c>
       <c r="B44" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>136774429</v>
       </c>
       <c r="B45" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>136774444</v>
       </c>
       <c r="B46" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>136774456</v>
       </c>
       <c r="B47" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>136774518</v>
       </c>
       <c r="B48" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>136774539</v>
       </c>
       <c r="B49" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>136774579</v>
       </c>
       <c r="B50" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>136819122</v>
       </c>
       <c r="B51" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136819195</v>
       </c>
       <c r="B52" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>136819203</v>
       </c>
       <c r="B53" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136819212</v>
       </c>
       <c r="B54" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>136819236</v>
       </c>
       <c r="B55" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136774567</v>
       </c>
       <c r="B3" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>136774732</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
+        <v>57328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>136774596</v>
       </c>
       <c r="B17" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>136819177</v>
       </c>
       <c r="B18" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>136819277</v>
       </c>
       <c r="B19" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>136819371</v>
       </c>
       <c r="B20" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>136819405</v>
       </c>
       <c r="B21" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>136819440</v>
       </c>
       <c r="B22" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>136774602</v>
       </c>
       <c r="B23" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>111473</v>
+        <v>111475</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>111473</v>
+        <v>111475</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
         <v>136774259</v>
       </c>
       <c r="B40" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>136774284</v>
       </c>
       <c r="B41" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>136774318</v>
       </c>
       <c r="B42" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>136774328</v>
       </c>
       <c r="B43" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>136774398</v>
       </c>
       <c r="B44" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>136774429</v>
       </c>
       <c r="B45" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>136774444</v>
       </c>
       <c r="B46" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>136774456</v>
       </c>
       <c r="B47" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>136774518</v>
       </c>
       <c r="B48" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>136774539</v>
       </c>
       <c r="B49" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>136774579</v>
       </c>
       <c r="B50" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>136819122</v>
       </c>
       <c r="B51" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>136819195</v>
       </c>
       <c r="B52" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>136819203</v>
       </c>
       <c r="B53" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>136819212</v>
       </c>
       <c r="B54" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>136819236</v>
       </c>
       <c r="B55" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -1522,11 +1522,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>sträckande</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -2454,11 +2450,7 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2568,11 +2560,7 @@
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2682,11 +2670,7 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2796,11 +2780,7 @@
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2910,11 +2890,7 @@
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3024,11 +3000,7 @@
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3134,11 +3106,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136774567</v>
       </c>
       <c r="B3" t="n">
-        <v>92823</v>
+        <v>92826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>111475</v>
+        <v>111481</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>111475</v>
+        <v>111481</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>136774259</v>
       </c>
       <c r="B40" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>136774284</v>
       </c>
       <c r="B41" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>136774318</v>
       </c>
       <c r="B42" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>136774328</v>
       </c>
       <c r="B43" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>136774398</v>
       </c>
       <c r="B44" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>136774429</v>
       </c>
       <c r="B45" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>136774444</v>
       </c>
       <c r="B46" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>136774456</v>
       </c>
       <c r="B47" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>136774518</v>
       </c>
       <c r="B48" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>136774539</v>
       </c>
       <c r="B49" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>136774579</v>
       </c>
       <c r="B50" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>136819122</v>
       </c>
       <c r="B51" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>136819195</v>
       </c>
       <c r="B52" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>136819203</v>
       </c>
       <c r="B53" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>136819212</v>
       </c>
       <c r="B54" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>136819236</v>
       </c>
       <c r="B55" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136774567</v>
       </c>
       <c r="B3" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>136774732</v>
       </c>
       <c r="B9" t="n">
-        <v>57328</v>
+        <v>57338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136774596</v>
       </c>
       <c r="B17" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136819177</v>
       </c>
       <c r="B18" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>136819277</v>
       </c>
       <c r="B19" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136819371</v>
       </c>
       <c r="B20" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136819405</v>
       </c>
       <c r="B21" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>136819440</v>
       </c>
       <c r="B22" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>136774602</v>
       </c>
       <c r="B23" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>111481</v>
+        <v>111503</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>111481</v>
+        <v>111503</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>136774259</v>
       </c>
       <c r="B40" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>136774284</v>
       </c>
       <c r="B41" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>136774318</v>
       </c>
       <c r="B42" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>136774328</v>
       </c>
       <c r="B43" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>136774398</v>
       </c>
       <c r="B44" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>136774429</v>
       </c>
       <c r="B45" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>136774444</v>
       </c>
       <c r="B46" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>136774456</v>
       </c>
       <c r="B47" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>136774518</v>
       </c>
       <c r="B48" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>136774539</v>
       </c>
       <c r="B49" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>136774579</v>
       </c>
       <c r="B50" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>136819122</v>
       </c>
       <c r="B51" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>136819195</v>
       </c>
       <c r="B52" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>136819203</v>
       </c>
       <c r="B53" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>136819212</v>
       </c>
       <c r="B54" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>136819236</v>
       </c>
       <c r="B55" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136774567</v>
       </c>
       <c r="B3" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>111503</v>
+        <v>111504</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>111503</v>
+        <v>111504</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>136774259</v>
       </c>
       <c r="B40" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>136774284</v>
       </c>
       <c r="B41" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>136774318</v>
       </c>
       <c r="B42" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>136774328</v>
       </c>
       <c r="B43" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>136774398</v>
       </c>
       <c r="B44" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>136774429</v>
       </c>
       <c r="B45" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>136774444</v>
       </c>
       <c r="B46" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>136774456</v>
       </c>
       <c r="B47" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>136774518</v>
       </c>
       <c r="B48" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>136774539</v>
       </c>
       <c r="B49" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>136774579</v>
       </c>
       <c r="B50" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>136819122</v>
       </c>
       <c r="B51" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>136819195</v>
       </c>
       <c r="B52" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>136819203</v>
       </c>
       <c r="B53" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>136819212</v>
       </c>
       <c r="B54" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>136819236</v>
       </c>
       <c r="B55" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136774567</v>
       </c>
       <c r="B3" t="n">
-        <v>92837</v>
+        <v>92840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>136774732</v>
       </c>
       <c r="B9" t="n">
-        <v>57338</v>
+        <v>57339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>136774596</v>
       </c>
       <c r="B17" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136819177</v>
       </c>
       <c r="B18" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>136819277</v>
       </c>
       <c r="B19" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136819371</v>
       </c>
       <c r="B20" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136819405</v>
       </c>
       <c r="B21" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>136819440</v>
       </c>
       <c r="B22" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>136774602</v>
       </c>
       <c r="B23" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>111504</v>
+        <v>111509</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>111504</v>
+        <v>111509</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>136774259</v>
       </c>
       <c r="B40" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>136774284</v>
       </c>
       <c r="B41" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>136774318</v>
       </c>
       <c r="B42" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>136774328</v>
       </c>
       <c r="B43" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>136774398</v>
       </c>
       <c r="B44" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>136774429</v>
       </c>
       <c r="B45" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>136774444</v>
       </c>
       <c r="B46" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>136774456</v>
       </c>
       <c r="B47" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>136774518</v>
       </c>
       <c r="B48" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>136774539</v>
       </c>
       <c r="B49" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>136774579</v>
       </c>
       <c r="B50" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>136819122</v>
       </c>
       <c r="B51" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>136819195</v>
       </c>
       <c r="B52" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>136819203</v>
       </c>
       <c r="B53" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>136819212</v>
       </c>
       <c r="B54" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>136819236</v>
       </c>
       <c r="B55" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>136774567</v>
       </c>
       <c r="B3" t="n">
-        <v>92840</v>
+        <v>92842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>111509</v>
+        <v>111512</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>111509</v>
+        <v>111512</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>136774259</v>
       </c>
       <c r="B40" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>136774284</v>
       </c>
       <c r="B41" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>136774318</v>
       </c>
       <c r="B42" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>136774328</v>
       </c>
       <c r="B43" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>136774398</v>
       </c>
       <c r="B44" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>136774429</v>
       </c>
       <c r="B45" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>136774444</v>
       </c>
       <c r="B46" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>136774456</v>
       </c>
       <c r="B47" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>136774518</v>
       </c>
       <c r="B48" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>136774539</v>
       </c>
       <c r="B49" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>136774579</v>
       </c>
       <c r="B50" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>136819122</v>
       </c>
       <c r="B51" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>136819195</v>
       </c>
       <c r="B52" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>136819203</v>
       </c>
       <c r="B53" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>136819212</v>
       </c>
       <c r="B54" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>136819236</v>
       </c>
       <c r="B55" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -2528,7 +2528,7 @@
         <v>136819177</v>
       </c>
       <c r="B18" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>136819277</v>
       </c>
       <c r="B19" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>136819371</v>
       </c>
       <c r="B20" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136819405</v>
       </c>
       <c r="B21" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>136819440</v>
       </c>
       <c r="B22" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>111512</v>
+        <v>111518</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>111512</v>
+        <v>111518</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>136819122</v>
       </c>
       <c r="B51" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>136819195</v>
       </c>
       <c r="B52" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>136819203</v>
       </c>
       <c r="B53" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>136819212</v>
       </c>
       <c r="B54" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>136819236</v>
       </c>
       <c r="B55" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 51234-2025 artfynd.xlsx
+++ b/artfynd/A 51234-2025 artfynd.xlsx
@@ -3753,7 +3753,7 @@
         <v>136819156</v>
       </c>
       <c r="B29" t="n">
-        <v>111518</v>
+        <v>111519</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>136819298</v>
       </c>
       <c r="B30" t="n">
-        <v>111518</v>
+        <v>111519</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
